--- a/data/trans_dic/P15B_tráfico-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15B_tráfico-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,22; 69,13</t>
+          <t>33,95; 68,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,12; 57,96</t>
+          <t>31,05; 56,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 43,16</t>
+          <t>16,31; 45,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,44</t>
+          <t>0,0; 57,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 72,28</t>
+          <t>16,93; 72,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,16; 58,98</t>
+          <t>26,99; 61,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,58; 58,1</t>
+          <t>15,32; 57,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,86; 93,06</t>
+          <t>39,28; 92,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,52; 64,61</t>
+          <t>35,22; 63,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,27; 54,8</t>
+          <t>34,57; 54,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,27; 43,0</t>
+          <t>20,5; 42,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 76,11</t>
+          <t>20,92; 68,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 49,87</t>
+          <t>16,76; 48,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 37,23</t>
+          <t>15,82; 35,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 40,7</t>
+          <t>15,93; 42,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,77; 73,5</t>
+          <t>20,2; 67,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 57,9</t>
+          <t>15,47; 59,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,13; 52,08</t>
+          <t>18,07; 50,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 61,46</t>
+          <t>20,57; 61,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 52,42</t>
+          <t>4,89; 46,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,1; 45,22</t>
+          <t>20,15; 45,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,57; 36,29</t>
+          <t>19,22; 35,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,24; 42,01</t>
+          <t>20,75; 43,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 58,81</t>
+          <t>18,06; 55,32</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 46,68</t>
+          <t>5,67; 46,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,01; 44,46</t>
+          <t>17,33; 44,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,14; 42,04</t>
+          <t>12,41; 43,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,32; 53,32</t>
+          <t>20,21; 54,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 46,79</t>
+          <t>6,95; 49,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 39,85</t>
+          <t>9,86; 40,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 43,5</t>
+          <t>7,22; 42,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,62; 54,82</t>
+          <t>22,7; 51,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 38,59</t>
+          <t>9,47; 39,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,81; 38,02</t>
+          <t>18,6; 38,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 36,65</t>
+          <t>13,36; 35,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,06; 48,33</t>
+          <t>25,35; 48,96</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,23</t>
+          <t>0,0; 42,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 21,53</t>
+          <t>2,54; 21,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 34,47</t>
+          <t>3,64; 31,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 42,86</t>
+          <t>19,18; 45,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 72,81</t>
+          <t>11,72; 73,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 33,92</t>
+          <t>6,22; 35,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 57,87</t>
+          <t>15,66; 57,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 26,15</t>
+          <t>6,86; 27,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 44,29</t>
+          <t>10,34; 46,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 22,88</t>
+          <t>5,77; 23,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 36,65</t>
+          <t>12,52; 37,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 32,52</t>
+          <t>16,39; 34,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,63</t>
+          <t>0,0; 58,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,72</t>
+          <t>0,0; 43,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,21</t>
+          <t>7,23; 54,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 40,37</t>
+          <t>10,43; 38,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 26,93</t>
+          <t>4,87; 26,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,82</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 32,22</t>
+          <t>10,92; 31,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,38</t>
+          <t>0,0; 31,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 25,98</t>
+          <t>5,7; 25,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 22,17</t>
+          <t>2,36; 21,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,4; 30,0</t>
+          <t>14,09; 31,32</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,89</t>
+          <t>0,0; 81,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,3</t>
+          <t>0,0; 47,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 34,02</t>
+          <t>7,96; 41,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,21</t>
+          <t>0,0; 54,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,27</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,24</t>
+          <t>0,0; 18,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 25,84</t>
+          <t>7,35; 25,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 49,92</t>
+          <t>6,17; 47,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 26,8</t>
+          <t>4,62; 26,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 13,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,71; 22,58</t>
+          <t>10,07; 26,23</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,96</t>
+          <t>0,0; 83,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 28,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,07</t>
+          <t>0,0; 22,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,91</t>
+          <t>0,0; 21,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 12,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,62</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,13</t>
+          <t>2,0; 11,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 28,57</t>
+          <t>2,85; 27,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,73</t>
+          <t>1,44; 12,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,0; 12,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,79</t>
+          <t>1,54; 8,55</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,44; 42,65</t>
+          <t>23,93; 41,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,63; 31,13</t>
+          <t>20,01; 31,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,73</t>
+          <t>15,98; 28,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,85; 35,57</t>
+          <t>20,99; 34,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,73; 29,85</t>
+          <t>13,58; 30,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,24</t>
+          <t>13,89; 24,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,19</t>
+          <t>12,07; 23,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,84; 28,19</t>
+          <t>16,69; 28,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,43; 33,86</t>
+          <t>22,05; 34,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,81; 26,05</t>
+          <t>19,02; 26,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,52; 23,7</t>
+          <t>15,93; 23,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 29,46</t>
+          <t>20,02; 29,06</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>18823</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11873; 23309</t>
+          <t>11446; 23023</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18851; 34016</t>
+          <t>18222; 32970</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6811; 18525</t>
+          <t>7000; 19332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 15777</t>
+          <t>0; 11889</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1782; 7652</t>
+          <t>1793; 7715</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8601; 18682</t>
+          <t>8549; 19390</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2846; 10611</t>
+          <t>2798; 10590</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8541; 18545</t>
+          <t>8875; 20915</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15292; 28622</t>
+          <t>15602; 27912</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30968; 49518</t>
+          <t>31240; 49442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12401; 26308</t>
+          <t>12546; 26094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10746; 29731</t>
+          <t>9058; 29741</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>17280</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5905; 17424</t>
+          <t>5855; 16976</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13023; 30645</t>
+          <t>13024; 28999</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7874; 20697</t>
+          <t>8099; 21413</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5391; 20041</t>
+          <t>6706; 22478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2804; 10742</t>
+          <t>2870; 11081</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6516; 19805</t>
+          <t>6872; 19343</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4632; 13938</t>
+          <t>4665; 13944</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>993; 7849</t>
+          <t>751; 7099</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10753; 24188</t>
+          <t>10778; 24354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23555; 43670</t>
+          <t>23137; 42737</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14885; 30889</t>
+          <t>15255; 31937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8133; 24843</t>
+          <t>8763; 26847</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>25020</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>853; 6970</t>
+          <t>847; 6941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10189; 25147</t>
+          <t>9801; 25146</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4711; 15074</t>
+          <t>4448; 15479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7518; 19731</t>
+          <t>7791; 21160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>887; 6278</t>
+          <t>932; 6598</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2875; 11711</t>
+          <t>2896; 11786</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1859; 10895</t>
+          <t>1809; 10618</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6903; 15367</t>
+          <t>6917; 15828</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1920; 10939</t>
+          <t>2683; 11248</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15307; 32681</t>
+          <t>15987; 32858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8740; 22321</t>
+          <t>8140; 21496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16301; 31432</t>
+          <t>17496; 33792</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>21897</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9618</t>
+          <t>0; 8357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>958; 7999</t>
+          <t>943; 8106</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1044; 9939</t>
+          <t>1048; 8937</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8024; 21329</t>
+          <t>10514; 24726</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1104; 7037</t>
+          <t>1133; 7084</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2241; 11881</t>
+          <t>2181; 12383</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4078; 14171</t>
+          <t>3835; 14081</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1598; 7683</t>
+          <t>2236; 9088</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2678; 12934</t>
+          <t>3021; 13666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4150; 16512</t>
+          <t>4165; 17104</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6383; 19541</t>
+          <t>6675; 20006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11035; 25740</t>
+          <t>14328; 30248</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>14828</t>
         </is>
       </c>
     </row>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5400</t>
+          <t>0; 5507</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5649</t>
+          <t>0; 5666</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7583</t>
+          <t>1011; 7649</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2899; 11680</t>
+          <t>3285; 12177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2925,37 +2925,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2004; 11245</t>
+          <t>2035; 11125</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4194</t>
+          <t>0; 4901</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3765; 11403</t>
+          <t>4182; 12037</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6230</t>
+          <t>0; 6076</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3184; 14204</t>
+          <t>3114; 13696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1013; 9830</t>
+          <t>1047; 9705</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8617; 19296</t>
+          <t>9834; 21861</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>9181</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3810</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 8183</t>
+          <t>0; 8139</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3123,47 +3123,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>614; 5541</t>
+          <t>1443; 7489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4120</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5894</t>
+          <t>0; 5863</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 5508</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2728; 8513</t>
+          <t>2663; 9181</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>853; 6872</t>
+          <t>850; 6542</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1024; 11424</t>
+          <t>1967; 11151</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5246</t>
+          <t>0; 5351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4290; 11114</t>
+          <t>5471; 14254</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3353</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4566</t>
+          <t>0; 4925</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6245</t>
+          <t>0; 6286</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 3296</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1538</t>
+          <t>0; 1964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4951</t>
+          <t>0; 4886</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7692</t>
+          <t>0; 6625</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6042</t>
+          <t>0; 6581</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1059; 5894</t>
+          <t>1134; 6722</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>814; 8151</t>
+          <t>814; 7904</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1108; 9703</t>
+          <t>1100; 9759</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 7735</t>
+          <t>0; 7153</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1119; 6476</t>
+          <t>1228; 6815</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>110382</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30076; 52497</t>
+          <t>29457; 50560</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>59210; 89346</t>
+          <t>57422; 89055</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31443; 54840</t>
+          <t>31603; 56501</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39525; 70825</t>
+          <t>46168; 76711</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12875; 28002</t>
+          <t>12735; 28731</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35916; 61910</t>
+          <t>35480; 61417</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23578; 44404</t>
+          <t>23115; 44219</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>35970; 60207</t>
+          <t>38760; 66540</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>46470; 73427</t>
+          <t>47830; 75745</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>102019; 141291</t>
+          <t>103161; 144262</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60415; 92239</t>
+          <t>61994; 91738</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>81571; 121571</t>
+          <t>90501; 131372</t>
         </is>
       </c>
     </row>
